--- a/data/trans_dic/P33_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,37; 75,67</t>
+          <t>70,23; 75,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,33; 68,49</t>
+          <t>61,79; 68,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,18; 73,45</t>
+          <t>66,99; 73,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,43; 70,23</t>
+          <t>62,68; 70,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,07; 68,21</t>
+          <t>62,82; 67,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,72; 59,27</t>
+          <t>53,99; 59,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,39; 62,85</t>
+          <t>56,81; 63,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,38; 62,73</t>
+          <t>57,13; 62,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,05; 70,91</t>
+          <t>66,97; 70,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,11; 62,31</t>
+          <t>58,27; 62,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,09; 66,9</t>
+          <t>62,03; 66,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,33; 64,73</t>
+          <t>60,45; 64,91</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,2; 87,6</t>
+          <t>84,22; 87,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,65; 79,63</t>
+          <t>75,71; 79,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,57; 80,24</t>
+          <t>76,42; 80,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,99; 86,76</t>
+          <t>75,97; 87,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,26; 84,11</t>
+          <t>80,13; 83,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,97; 74,44</t>
+          <t>69,96; 74,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,94; 77,0</t>
+          <t>73,17; 76,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,68; 73,9</t>
+          <t>48,48; 74,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 85,46</t>
+          <t>82,77; 85,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,5; 76,52</t>
+          <t>73,5; 76,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,47; 78,17</t>
+          <t>75,3; 78,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,6; 77,54</t>
+          <t>61,27; 77,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,11; 86,39</t>
+          <t>80,05; 86,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,14; 81,25</t>
+          <t>72,77; 81,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,68; 82,64</t>
+          <t>75,47; 82,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,43; 80,35</t>
+          <t>71,71; 80,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,87; 86,4</t>
+          <t>79,82; 86,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,44; 84,44</t>
+          <t>77,18; 85,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,93; 82,26</t>
+          <t>74,96; 82,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,07; 75,55</t>
+          <t>69,26; 75,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,92; 85,82</t>
+          <t>81,17; 85,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76,52; 81,99</t>
+          <t>76,51; 81,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,36; 81,49</t>
+          <t>76,29; 81,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,73; 76,88</t>
+          <t>71,77; 76,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,16; 82,8</t>
+          <t>79,98; 82,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,52; 75,65</t>
+          <t>72,65; 75,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,32; 78,26</t>
+          <t>75,2; 78,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,42; 82,94</t>
+          <t>74,57; 81,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,51; 77,4</t>
+          <t>74,42; 77,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,92; 68,92</t>
+          <t>65,82; 68,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,99; 73,08</t>
+          <t>69,87; 73,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,39; 70,67</t>
+          <t>51,74; 70,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,7; 79,69</t>
+          <t>77,61; 79,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,9</t>
+          <t>69,56; 71,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,02; 75,29</t>
+          <t>72,92; 75,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,28; 74,2</t>
+          <t>64,3; 74,41</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>717319; 771320</t>
+          <t>715849; 770460</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>604121; 663796</t>
+          <t>598836; 663580</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505445; 552574</t>
+          <t>503990; 552436</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311994; 350991</t>
+          <t>313265; 350918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>825141; 892411</t>
+          <t>821955; 888029</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>717008; 791135</t>
+          <t>720591; 793971</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>556060; 619792</t>
+          <t>560160; 625834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>413669; 452286</t>
+          <t>411879; 450684</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1560688; 1650592</t>
+          <t>1558857; 1648372</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1338750; 1435513</t>
+          <t>1342535; 1434820</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1079398; 1163011</t>
+          <t>1078417; 1157105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>736454; 790178</t>
+          <t>737953; 792333</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1402161; 1458918</t>
+          <t>1402471; 1460850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1479928; 1557704</t>
+          <t>1481020; 1555293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1586146; 1662305</t>
+          <t>1583051; 1658541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1680146; 1918211</t>
+          <t>1679512; 1925836</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1262784; 1323333</t>
+          <t>1260626; 1320486</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1225551; 1303776</t>
+          <t>1225393; 1302014</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1445813; 1526412</t>
+          <t>1450476; 1526268</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1059103; 1607844</t>
+          <t>1054759; 1612874</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2683318; 2767718</t>
+          <t>2680751; 2764951</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2724999; 2837037</t>
+          <t>2725328; 2842446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3059583; 3169142</t>
+          <t>3052811; 3168567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2746093; 3401234</t>
+          <t>2687633; 3398512</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>436532; 470745</t>
+          <t>436200; 472008</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>351939; 390974</t>
+          <t>350139; 389777</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>408391; 451949</t>
+          <t>412760; 453189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>455926; 512881</t>
+          <t>457727; 513229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>379756; 410821</t>
+          <t>379505; 411829</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>355168; 387278</t>
+          <t>353969; 390212</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>411459; 451704</t>
+          <t>411655; 450312</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>451877; 494257</t>
+          <t>453138; 493058</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>825707; 875693</t>
+          <t>828307; 873958</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>719127; 770515</t>
+          <t>719092; 770383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>836891; 893101</t>
+          <t>836189; 888312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>927135; 993691</t>
+          <t>927677; 992982</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2588708; 2674029</t>
+          <t>2582930; 2674378</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2470376; 2577049</t>
+          <t>2474890; 2581412</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2538860; 2637967</t>
+          <t>2535032; 2633441</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2492358; 2777745</t>
+          <t>2497232; 2742721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2501367; 2598566</t>
+          <t>2498276; 2596209</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2336731; 2442970</t>
+          <t>2333200; 2445622</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2462005; 2570547</t>
+          <t>2457747; 2573138</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1895744; 2509408</t>
+          <t>1837181; 2499740</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5118185; 5248700</t>
+          <t>5112156; 5243770</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4834427; 4998194</t>
+          <t>4835130; 5000791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5029752; 5186334</t>
+          <t>5023181; 5177445</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4435516; 5119581</t>
+          <t>4436756; 5134466</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P33_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,23; 75,59</t>
+          <t>70,2; 75,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,79; 68,47</t>
+          <t>62,06; 68,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,99; 73,43</t>
+          <t>66,97; 73,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,68; 70,22</t>
+          <t>64,01; 71,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,82; 67,87</t>
+          <t>63,19; 68,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,99; 59,49</t>
+          <t>53,56; 59,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,81; 63,47</t>
+          <t>56,43; 63,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,13; 62,51</t>
+          <t>57,39; 62,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,97; 70,81</t>
+          <t>66,81; 70,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,27; 62,28</t>
+          <t>58,16; 62,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,03; 66,56</t>
+          <t>62,05; 66,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,45; 64,91</t>
+          <t>60,79; 65,57</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,22; 87,72</t>
+          <t>83,99; 87,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75,71; 79,51</t>
+          <t>75,6; 79,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,42; 80,06</t>
+          <t>76,53; 80,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,97; 87,11</t>
+          <t>74,77; 78,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,13; 83,93</t>
+          <t>80,3; 84,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,96; 74,34</t>
+          <t>70,02; 74,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,17; 76,99</t>
+          <t>72,82; 77,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,48; 74,13</t>
+          <t>69,81; 73,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,77; 85,37</t>
+          <t>82,76; 85,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,5; 76,66</t>
+          <t>73,51; 76,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,3; 78,16</t>
+          <t>75,48; 78,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,27; 77,47</t>
+          <t>72,87; 75,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,05; 86,62</t>
+          <t>80,03; 86,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,77; 81,0</t>
+          <t>73,1; 81,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,47; 82,87</t>
+          <t>75,3; 82,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,71; 80,41</t>
+          <t>73,97; 80,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,82; 86,61</t>
+          <t>79,81; 86,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,18; 85,08</t>
+          <t>77,05; 84,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,96; 82,0</t>
+          <t>74,82; 82,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,26; 75,37</t>
+          <t>69,3; 75,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,17; 85,65</t>
+          <t>80,75; 85,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76,51; 81,97</t>
+          <t>76,14; 81,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,29; 81,05</t>
+          <t>76,28; 81,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,77; 76,83</t>
+          <t>72,61; 77,29</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,98; 82,81</t>
+          <t>79,88; 82,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,65; 75,78</t>
+          <t>72,47; 75,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,2; 78,12</t>
+          <t>75,42; 78,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,57; 81,9</t>
+          <t>73,9; 77,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,42; 77,33</t>
+          <t>74,35; 77,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,82; 68,99</t>
+          <t>65,78; 69,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,87; 73,15</t>
+          <t>69,97; 73,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,74; 70,4</t>
+          <t>68,03; 70,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,61; 79,61</t>
+          <t>77,7; 79,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,56; 71,94</t>
+          <t>69,49; 71,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,92; 75,16</t>
+          <t>73,08; 75,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,3; 74,41</t>
+          <t>71,33; 73,32</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332348</t>
+          <t>379775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>431794</t>
+          <t>473227</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>764142</t>
+          <t>853001</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>715849; 770460</t>
+          <t>715556; 772268</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>598836; 663580</t>
+          <t>601460; 663947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503990; 552436</t>
+          <t>503832; 553954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313265; 350918</t>
+          <t>359255; 399716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>821955; 888029</t>
+          <t>826731; 894086</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>720591; 793971</t>
+          <t>714857; 792522</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>560160; 625834</t>
+          <t>556431; 622795</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>411879; 450684</t>
+          <t>451085; 494334</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1558857; 1648372</t>
+          <t>1555180; 1649059</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1342535; 1434820</t>
+          <t>1339992; 1439009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1078417; 1157105</t>
+          <t>1078776; 1160980</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>737953; 792333</t>
+          <t>818959; 883355</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1754258</t>
+          <t>1653422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1435570</t>
+          <t>1505228</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3189827</t>
+          <t>3158650</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1402471; 1460850</t>
+          <t>1398735; 1456744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1481020; 1555293</t>
+          <t>1478869; 1556699</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1583051; 1658541</t>
+          <t>1585382; 1664064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1679512; 1925836</t>
+          <t>1610353; 1691870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1260626; 1320486</t>
+          <t>1263287; 1322950</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1225393; 1302014</t>
+          <t>1226502; 1300938</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1450476; 1526268</t>
+          <t>1443547; 1526597</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1054759; 1612874</t>
+          <t>1468393; 1542559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2680751; 2764951</t>
+          <t>2680425; 2766418</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2725328; 2842446</t>
+          <t>2725417; 2841073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3052811; 3168567</t>
+          <t>3060000; 3169002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2687633; 3398512</t>
+          <t>3101957; 3217435</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488381</t>
+          <t>544408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>473788</t>
+          <t>527390</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>962168</t>
+          <t>1071798</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>436200; 472008</t>
+          <t>436085; 472536</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>350139; 389777</t>
+          <t>351732; 391761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>412760; 453189</t>
+          <t>411832; 452763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>457727; 513229</t>
+          <t>518901; 567421</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>379505; 411829</t>
+          <t>379468; 410916</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>353969; 390212</t>
+          <t>353359; 388054</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>411655; 450312</t>
+          <t>410840; 450403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>453138; 493058</t>
+          <t>504529; 548298</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>828307; 873958</t>
+          <t>823938; 875640</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>719092; 770383</t>
+          <t>715528; 769090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>836189; 888312</t>
+          <t>836075; 892491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>927677; 992982</t>
+          <t>1038073; 1104979</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2574986</t>
+          <t>2577605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2341151</t>
+          <t>2505844</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4916137</t>
+          <t>5083449</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2582930; 2674378</t>
+          <t>2579842; 2675558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2474890; 2581412</t>
+          <t>2468881; 2572878</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2535032; 2633441</t>
+          <t>2542270; 2637158</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2497232; 2742721</t>
+          <t>2524866; 2632976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2498276; 2596209</t>
+          <t>2496057; 2595772</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2333200; 2445622</t>
+          <t>2331898; 2449052</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2457747; 2573138</t>
+          <t>2461367; 2568423</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1837181; 2499740</t>
+          <t>2460917; 2557318</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5112156; 5243770</t>
+          <t>5117800; 5248057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4835130; 5000791</t>
+          <t>4830865; 4986472</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5023181; 5177445</t>
+          <t>5033731; 5171633</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4436756; 5134466</t>
+          <t>5017040; 5156933</t>
         </is>
       </c>
     </row>
